--- a/Team-Data/2014-15/3-19-2014-15.xlsx
+++ b/Team-Data/2014-15/3-19-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>5.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE2" t="n">
         <v>2</v>
@@ -775,7 +842,7 @@
         <v>15</v>
       </c>
       <c r="AP2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ2" t="n">
         <v>6</v>
@@ -799,7 +866,7 @@
         <v>5</v>
       </c>
       <c r="AX2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AY2" t="n">
         <v>17</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-19-2014-15</t>
+          <t>2015-03-19</t>
         </is>
       </c>
     </row>
@@ -921,19 +988,19 @@
         <v>-0.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AE3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF3" t="n">
         <v>18</v>
       </c>
       <c r="AG3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI3" t="n">
         <v>5</v>
@@ -966,10 +1033,10 @@
         <v>11</v>
       </c>
       <c r="AS3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU3" t="n">
         <v>4</v>
@@ -981,10 +1048,10 @@
         <v>11</v>
       </c>
       <c r="AX3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AY3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ3" t="n">
         <v>19</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-19-2014-15</t>
+          <t>2015-03-19</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-3.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE4" t="n">
         <v>22</v>
@@ -1124,7 +1191,7 @@
         <v>23</v>
       </c>
       <c r="AK4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL4" t="n">
         <v>24</v>
@@ -1139,7 +1206,7 @@
         <v>21</v>
       </c>
       <c r="AP4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ4" t="n">
         <v>23</v>
@@ -1151,7 +1218,7 @@
         <v>20</v>
       </c>
       <c r="AT4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU4" t="n">
         <v>27</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-19-2014-15</t>
+          <t>2015-03-19</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-2.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE5" t="n">
         <v>21</v>
@@ -1318,13 +1385,13 @@
         <v>30</v>
       </c>
       <c r="AO5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP5" t="n">
         <v>14</v>
       </c>
       <c r="AQ5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR5" t="n">
         <v>25</v>
@@ -1348,7 +1415,7 @@
         <v>8</v>
       </c>
       <c r="AY5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ5" t="n">
         <v>4</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-19-2014-15</t>
+          <t>2015-03-19</t>
         </is>
       </c>
     </row>
@@ -1467,10 +1534,10 @@
         <v>2.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF6" t="n">
         <v>11</v>
@@ -1479,7 +1546,7 @@
         <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI6" t="n">
         <v>23</v>
@@ -1503,13 +1570,13 @@
         <v>2</v>
       </c>
       <c r="AP6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ6" t="n">
         <v>2</v>
       </c>
       <c r="AR6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS6" t="n">
         <v>6</v>
@@ -1521,22 +1588,22 @@
         <v>16</v>
       </c>
       <c r="AV6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW6" t="n">
         <v>29</v>
       </c>
       <c r="AX6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ6" t="n">
         <v>3</v>
       </c>
       <c r="BA6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB6" t="n">
         <v>14</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-19-2014-15</t>
+          <t>2015-03-19</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1728,7 @@
         <v>8</v>
       </c>
       <c r="AH7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI7" t="n">
         <v>14</v>
@@ -1679,7 +1746,7 @@
         <v>4</v>
       </c>
       <c r="AN7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO7" t="n">
         <v>6</v>
@@ -1688,7 +1755,7 @@
         <v>9</v>
       </c>
       <c r="AQ7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR7" t="n">
         <v>12</v>
@@ -1712,7 +1779,7 @@
         <v>26</v>
       </c>
       <c r="AY7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ7" t="n">
         <v>5</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-19-2014-15</t>
+          <t>2015-03-19</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E8" t="n">
         <v>44</v>
       </c>
       <c r="F8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G8" t="n">
-        <v>0.647</v>
+        <v>0.638</v>
       </c>
       <c r="H8" t="n">
         <v>48.4</v>
@@ -1771,19 +1838,19 @@
         <v>39.5</v>
       </c>
       <c r="J8" t="n">
-        <v>85.59999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K8" t="n">
         <v>0.462</v>
       </c>
       <c r="L8" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="N8" t="n">
-        <v>0.354</v>
+        <v>0.355</v>
       </c>
       <c r="O8" t="n">
         <v>16.6</v>
@@ -1792,19 +1859,19 @@
         <v>21.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.757</v>
+        <v>0.758</v>
       </c>
       <c r="R8" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="S8" t="n">
-        <v>31.6</v>
+        <v>31.5</v>
       </c>
       <c r="T8" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="U8" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="V8" t="n">
         <v>12.8</v>
@@ -1828,10 +1895,10 @@
         <v>104.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1843,7 +1910,7 @@
         <v>6</v>
       </c>
       <c r="AH8" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
@@ -1867,19 +1934,19 @@
         <v>20</v>
       </c>
       <c r="AP8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR8" t="n">
         <v>19</v>
       </c>
       <c r="AS8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT8" t="n">
         <v>23</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>22</v>
       </c>
       <c r="AU8" t="n">
         <v>8</v>
@@ -1891,7 +1958,7 @@
         <v>8</v>
       </c>
       <c r="AX8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY8" t="n">
         <v>4</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-19-2014-15</t>
+          <t>2015-03-19</t>
         </is>
       </c>
     </row>
@@ -1935,52 +2002,52 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E9" t="n">
         <v>26</v>
       </c>
       <c r="F9" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G9" t="n">
-        <v>0.377</v>
+        <v>0.382</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
       </c>
       <c r="I9" t="n">
-        <v>37.4</v>
+        <v>37.3</v>
       </c>
       <c r="J9" t="n">
-        <v>86.8</v>
+        <v>86.7</v>
       </c>
       <c r="K9" t="n">
         <v>0.43</v>
       </c>
       <c r="L9" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="M9" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0.32</v>
+        <v>0.319</v>
       </c>
       <c r="O9" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="P9" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.731</v>
+        <v>0.733</v>
       </c>
       <c r="R9" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S9" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="T9" t="n">
         <v>44.8</v>
@@ -1998,22 +2065,22 @@
         <v>4.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="AA9" t="n">
         <v>20.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>100.3</v>
+        <v>100.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>-3.5</v>
+        <v>-3.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE9" t="n">
         <v>23</v>
@@ -2025,16 +2092,16 @@
         <v>23</v>
       </c>
       <c r="AH9" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AI9" t="n">
         <v>17</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL9" t="n">
         <v>15</v>
@@ -2073,10 +2140,10 @@
         <v>17</v>
       </c>
       <c r="AX9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AY9" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AZ9" t="n">
         <v>30</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-19-2014-15</t>
+          <t>2015-03-19</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-2</v>
       </c>
       <c r="AD10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2240,7 +2307,7 @@
         <v>1</v>
       </c>
       <c r="AS10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT10" t="n">
         <v>4</v>
@@ -2261,7 +2328,7 @@
         <v>18</v>
       </c>
       <c r="AZ10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA10" t="n">
         <v>22</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-19-2014-15</t>
+          <t>2015-03-19</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>10.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2389,13 +2456,13 @@
         <v>1</v>
       </c>
       <c r="AH11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI11" t="n">
         <v>1</v>
       </c>
       <c r="AJ11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK11" t="n">
         <v>1</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-19-2014-15</t>
+          <t>2015-03-19</t>
         </is>
       </c>
     </row>
@@ -2496,13 +2563,13 @@
         <v>48.4</v>
       </c>
       <c r="I12" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J12" t="n">
-        <v>84.3</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="L12" t="n">
         <v>11.5</v>
@@ -2511,28 +2578,28 @@
         <v>33.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0.343</v>
+        <v>0.344</v>
       </c>
       <c r="O12" t="n">
         <v>17.8</v>
       </c>
       <c r="P12" t="n">
-        <v>24.6</v>
+        <v>24.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.722</v>
+        <v>0.719</v>
       </c>
       <c r="R12" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S12" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T12" t="n">
         <v>43.7</v>
       </c>
       <c r="U12" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="V12" t="n">
         <v>16.7</v>
@@ -2541,25 +2608,25 @@
         <v>9.5</v>
       </c>
       <c r="X12" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y12" t="n">
         <v>5.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.2</v>
+        <v>103.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AE12" t="n">
         <v>4</v>
@@ -2577,7 +2644,7 @@
         <v>19</v>
       </c>
       <c r="AJ12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK12" t="n">
         <v>22</v>
@@ -2607,7 +2674,7 @@
         <v>21</v>
       </c>
       <c r="AT12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU12" t="n">
         <v>10</v>
@@ -2625,13 +2692,13 @@
         <v>26</v>
       </c>
       <c r="AZ12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA12" t="n">
         <v>11</v>
       </c>
       <c r="BB12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-19-2014-15</t>
+          <t>2015-03-19</t>
         </is>
       </c>
     </row>
@@ -2741,16 +2808,16 @@
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AE13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF13" t="n">
         <v>18</v>
       </c>
       <c r="AG13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH13" t="n">
         <v>18</v>
@@ -2780,7 +2847,7 @@
         <v>23</v>
       </c>
       <c r="AQ13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR13" t="n">
         <v>21</v>
@@ -2816,7 +2883,7 @@
         <v>24</v>
       </c>
       <c r="BC13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-19-2014-15</t>
+          <t>2015-03-19</t>
         </is>
       </c>
     </row>
@@ -2923,16 +2990,16 @@
         <v>5.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE14" t="n">
         <v>5</v>
       </c>
       <c r="AF14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH14" t="n">
         <v>29</v>
@@ -2965,7 +3032,7 @@
         <v>28</v>
       </c>
       <c r="AR14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-19-2014-15</t>
+          <t>2015-03-19</t>
         </is>
       </c>
     </row>
@@ -3042,13 +3109,13 @@
         <v>48.6</v>
       </c>
       <c r="I15" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J15" t="n">
         <v>86</v>
       </c>
       <c r="K15" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
       <c r="L15" t="n">
         <v>6.5</v>
@@ -3060,22 +3127,22 @@
         <v>0.344</v>
       </c>
       <c r="O15" t="n">
-        <v>17.3</v>
+        <v>17.6</v>
       </c>
       <c r="P15" t="n">
-        <v>23.3</v>
+        <v>23.7</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.741</v>
+        <v>0.746</v>
       </c>
       <c r="R15" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="S15" t="n">
-        <v>32.7</v>
+        <v>32.5</v>
       </c>
       <c r="T15" t="n">
-        <v>44.3</v>
+        <v>44.2</v>
       </c>
       <c r="U15" t="n">
         <v>20.9</v>
@@ -3090,28 +3157,28 @@
         <v>4.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="AB15" t="n">
-        <v>98.8</v>
+        <v>99</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.9</v>
+        <v>-6.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
       </c>
       <c r="AF15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG15" t="n">
         <v>27</v>
@@ -3126,7 +3193,7 @@
         <v>7</v>
       </c>
       <c r="AK15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL15" t="n">
         <v>25</v>
@@ -3141,16 +3208,16 @@
         <v>12</v>
       </c>
       <c r="AP15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AR15" t="n">
         <v>9</v>
       </c>
       <c r="AS15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT15" t="n">
         <v>9</v>
@@ -3162,7 +3229,7 @@
         <v>5</v>
       </c>
       <c r="AW15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX15" t="n">
         <v>21</v>
@@ -3171,13 +3238,13 @@
         <v>15</v>
       </c>
       <c r="AZ15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA15" t="n">
         <v>23</v>
       </c>
       <c r="BB15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-19-2014-15</t>
+          <t>2015-03-19</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>3.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3305,7 +3372,7 @@
         <v>12</v>
       </c>
       <c r="AJ16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK16" t="n">
         <v>10</v>
@@ -3323,7 +3390,7 @@
         <v>7</v>
       </c>
       <c r="AP16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ16" t="n">
         <v>4</v>
@@ -3338,7 +3405,7 @@
         <v>20</v>
       </c>
       <c r="AU16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV16" t="n">
         <v>6</v>
@@ -3350,7 +3417,7 @@
         <v>23</v>
       </c>
       <c r="AY16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ16" t="n">
         <v>9</v>
@@ -3359,7 +3426,7 @@
         <v>16</v>
       </c>
       <c r="BB16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC16" t="n">
         <v>8</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-19-2014-15</t>
+          <t>2015-03-19</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-2.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
@@ -3481,7 +3548,7 @@
         <v>17</v>
       </c>
       <c r="AH17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI17" t="n">
         <v>29</v>
@@ -3508,7 +3575,7 @@
         <v>10</v>
       </c>
       <c r="AQ17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR17" t="n">
         <v>29</v>
@@ -3541,7 +3608,7 @@
         <v>8</v>
       </c>
       <c r="BB17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC17" t="n">
         <v>21</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-19-2014-15</t>
+          <t>2015-03-19</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>0.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE18" t="n">
         <v>16</v>
@@ -3690,7 +3757,7 @@
         <v>25</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR18" t="n">
         <v>24</v>
@@ -3717,7 +3784,7 @@
         <v>14</v>
       </c>
       <c r="AZ18" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BA18" t="n">
         <v>20</v>
@@ -3726,7 +3793,7 @@
         <v>22</v>
       </c>
       <c r="BC18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-19-2014-15</t>
+          <t>2015-03-19</t>
         </is>
       </c>
     </row>
@@ -3755,19 +3822,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F19" t="n">
         <v>53</v>
       </c>
       <c r="G19" t="n">
-        <v>0.221</v>
+        <v>0.209</v>
       </c>
       <c r="H19" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="I19" t="n">
         <v>36.7</v>
@@ -3776,37 +3843,37 @@
         <v>84.3</v>
       </c>
       <c r="K19" t="n">
-        <v>0.435</v>
+        <v>0.436</v>
       </c>
       <c r="L19" t="n">
         <v>4.9</v>
       </c>
       <c r="M19" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0.33</v>
+        <v>0.332</v>
       </c>
       <c r="O19" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="P19" t="n">
         <v>25.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.767</v>
+        <v>0.766</v>
       </c>
       <c r="R19" t="n">
         <v>12.2</v>
       </c>
       <c r="S19" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="T19" t="n">
         <v>41.9</v>
       </c>
       <c r="U19" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="V19" t="n">
         <v>15</v>
@@ -3815,25 +3882,25 @@
         <v>8.300000000000001</v>
       </c>
       <c r="X19" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Y19" t="n">
         <v>5.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AA19" t="n">
         <v>21.4</v>
       </c>
       <c r="AB19" t="n">
-        <v>97.7</v>
+        <v>97.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>-8</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AD19" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AE19" t="n">
         <v>29</v>
@@ -3845,16 +3912,16 @@
         <v>29</v>
       </c>
       <c r="AH19" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI19" t="n">
         <v>21</v>
       </c>
       <c r="AJ19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL19" t="n">
         <v>30</v>
@@ -3863,13 +3930,13 @@
         <v>30</v>
       </c>
       <c r="AN19" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP19" t="n">
         <v>3</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>2</v>
       </c>
       <c r="AQ19" t="n">
         <v>12</v>
@@ -3884,7 +3951,7 @@
         <v>24</v>
       </c>
       <c r="AU19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV19" t="n">
         <v>23</v>
@@ -3902,7 +3969,7 @@
         <v>10</v>
       </c>
       <c r="BA19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB19" t="n">
         <v>21</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-19-2014-15</t>
+          <t>2015-03-19</t>
         </is>
       </c>
     </row>
@@ -3940,25 +4007,25 @@
         <v>67</v>
       </c>
       <c r="E20" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F20" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G20" t="n">
-        <v>0.537</v>
+        <v>0.552</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>37.8</v>
+        <v>38</v>
       </c>
       <c r="J20" t="n">
-        <v>82.90000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.456</v>
+        <v>0.457</v>
       </c>
       <c r="L20" t="n">
         <v>7</v>
@@ -3970,34 +4037,34 @@
         <v>0.36</v>
       </c>
       <c r="O20" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="P20" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.767</v>
+        <v>0.763</v>
       </c>
       <c r="R20" t="n">
-        <v>11.5</v>
+        <v>11.7</v>
       </c>
       <c r="S20" t="n">
         <v>32.1</v>
       </c>
       <c r="T20" t="n">
-        <v>43.6</v>
+        <v>43.9</v>
       </c>
       <c r="U20" t="n">
         <v>22</v>
       </c>
       <c r="V20" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="W20" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X20" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="Y20" t="n">
         <v>5.9</v>
@@ -4006,22 +4073,22 @@
         <v>18.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.3</v>
+        <v>99.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AE20" t="n">
         <v>14</v>
       </c>
       <c r="AF20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG20" t="n">
         <v>14</v>
@@ -4039,7 +4106,7 @@
         <v>11</v>
       </c>
       <c r="AL20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM20" t="n">
         <v>23</v>
@@ -4048,25 +4115,25 @@
         <v>9</v>
       </c>
       <c r="AO20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP20" t="n">
         <v>18</v>
       </c>
-      <c r="AP20" t="n">
-        <v>22</v>
-      </c>
       <c r="AQ20" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AR20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU20" t="n">
         <v>10</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>17</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>15</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>11</v>
       </c>
       <c r="AV20" t="n">
         <v>7</v>
@@ -4075,7 +4142,7 @@
         <v>25</v>
       </c>
       <c r="AX20" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AY20" t="n">
         <v>28</v>
@@ -4090,7 +4157,7 @@
         <v>16</v>
       </c>
       <c r="BC20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-19-2014-15</t>
+          <t>2015-03-19</t>
         </is>
       </c>
     </row>
@@ -4119,43 +4186,43 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E21" t="n">
         <v>14</v>
       </c>
       <c r="F21" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G21" t="n">
-        <v>0.206</v>
+        <v>0.209</v>
       </c>
       <c r="H21" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I21" t="n">
-        <v>35.6</v>
+        <v>35.5</v>
       </c>
       <c r="J21" t="n">
-        <v>82.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.43</v>
+        <v>0.431</v>
       </c>
       <c r="L21" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="M21" t="n">
         <v>19.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0.345</v>
+        <v>0.348</v>
       </c>
       <c r="O21" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="P21" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="Q21" t="n">
         <v>0.763</v>
@@ -4164,16 +4231,16 @@
         <v>10.8</v>
       </c>
       <c r="S21" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="T21" t="n">
-        <v>40.6</v>
+        <v>40.5</v>
       </c>
       <c r="U21" t="n">
         <v>21.4</v>
       </c>
       <c r="V21" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="W21" t="n">
         <v>7.1</v>
@@ -4188,37 +4255,37 @@
         <v>22</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="AB21" t="n">
         <v>92.40000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>-8.800000000000001</v>
+        <v>-8.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AE21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG21" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL21" t="n">
         <v>22</v>
@@ -4227,7 +4294,7 @@
         <v>21</v>
       </c>
       <c r="AN21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO21" t="n">
         <v>29</v>
@@ -4239,7 +4306,7 @@
         <v>15</v>
       </c>
       <c r="AR21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS21" t="n">
         <v>29</v>
@@ -4263,10 +4330,10 @@
         <v>8</v>
       </c>
       <c r="AZ21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA21" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BB21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-19-2014-15</t>
+          <t>2015-03-19</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>2.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE22" t="n">
         <v>13</v>
@@ -4409,7 +4476,7 @@
         <v>15</v>
       </c>
       <c r="AN22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO22" t="n">
         <v>5</v>
@@ -4418,7 +4485,7 @@
         <v>7</v>
       </c>
       <c r="AQ22" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AR22" t="n">
         <v>2</v>
@@ -4433,10 +4500,10 @@
         <v>22</v>
       </c>
       <c r="AV22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX22" t="n">
         <v>6</v>
@@ -4451,7 +4518,7 @@
         <v>14</v>
       </c>
       <c r="BB22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC22" t="n">
         <v>11</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-19-2014-15</t>
+          <t>2015-03-19</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E23" t="n">
         <v>21</v>
       </c>
       <c r="F23" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G23" t="n">
-        <v>0.304</v>
+        <v>0.3</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
@@ -4504,13 +4571,13 @@
         <v>82.3</v>
       </c>
       <c r="K23" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L23" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M23" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="N23" t="n">
         <v>0.354</v>
@@ -4522,19 +4589,19 @@
         <v>19.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.724</v>
+        <v>0.725</v>
       </c>
       <c r="R23" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="S23" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T23" t="n">
-        <v>41</v>
+        <v>41.2</v>
       </c>
       <c r="U23" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V23" t="n">
         <v>14.9</v>
@@ -4543,25 +4610,25 @@
         <v>7.9</v>
       </c>
       <c r="X23" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AA23" t="n">
         <v>18.2</v>
       </c>
       <c r="AB23" t="n">
-        <v>96</v>
+        <v>95.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.8</v>
+        <v>-6</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>26</v>
@@ -4573,7 +4640,7 @@
         <v>26</v>
       </c>
       <c r="AH23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI23" t="n">
         <v>16</v>
@@ -4582,10 +4649,10 @@
         <v>21</v>
       </c>
       <c r="AK23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM23" t="n">
         <v>22</v>
@@ -4600,34 +4667,34 @@
         <v>29</v>
       </c>
       <c r="AQ23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR23" t="n">
         <v>27</v>
       </c>
       <c r="AS23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT23" t="n">
         <v>27</v>
       </c>
       <c r="AU23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW23" t="n">
         <v>12</v>
       </c>
       <c r="AX23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AY23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AZ23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-19-2014-15</t>
+          <t>2015-03-19</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-9.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4785,7 +4852,7 @@
         <v>30</v>
       </c>
       <c r="AR24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AS24" t="n">
         <v>26</v>
@@ -4803,13 +4870,13 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA24" t="n">
         <v>17</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-19-2014-15</t>
+          <t>2015-03-19</t>
         </is>
       </c>
     </row>
@@ -4847,58 +4914,58 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E25" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F25" t="n">
         <v>33</v>
       </c>
       <c r="G25" t="n">
-        <v>0.522</v>
+        <v>0.515</v>
       </c>
       <c r="H25" t="n">
         <v>48.6</v>
       </c>
       <c r="I25" t="n">
-        <v>39.2</v>
+        <v>39.4</v>
       </c>
       <c r="J25" t="n">
         <v>86.3</v>
       </c>
       <c r="K25" t="n">
-        <v>0.455</v>
+        <v>0.456</v>
       </c>
       <c r="L25" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="M25" t="n">
         <v>25.9</v>
       </c>
       <c r="N25" t="n">
-        <v>0.348</v>
+        <v>0.351</v>
       </c>
       <c r="O25" t="n">
-        <v>16.7</v>
+        <v>16.8</v>
       </c>
       <c r="P25" t="n">
         <v>21.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.768</v>
+        <v>0.769</v>
       </c>
       <c r="R25" t="n">
         <v>11.1</v>
       </c>
       <c r="S25" t="n">
-        <v>32.3</v>
+        <v>32.1</v>
       </c>
       <c r="T25" t="n">
-        <v>43.4</v>
+        <v>43.2</v>
       </c>
       <c r="U25" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="V25" t="n">
         <v>15.2</v>
@@ -4907,28 +4974,28 @@
         <v>8.699999999999999</v>
       </c>
       <c r="X25" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y25" t="n">
         <v>4</v>
       </c>
       <c r="Z25" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AA25" t="n">
         <v>20.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>104.1</v>
+        <v>104.6</v>
       </c>
       <c r="AC25" t="n">
         <v>0.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AE25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF25" t="n">
         <v>15</v>
@@ -4943,40 +5010,40 @@
         <v>3</v>
       </c>
       <c r="AJ25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL25" t="n">
         <v>8</v>
       </c>
       <c r="AM25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO25" t="n">
         <v>17</v>
       </c>
       <c r="AP25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS25" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AT25" t="n">
         <v>17</v>
       </c>
       <c r="AU25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV25" t="n">
         <v>25</v>
@@ -4985,7 +5052,7 @@
         <v>7</v>
       </c>
       <c r="AX25" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AY25" t="n">
         <v>5</v>
@@ -4997,7 +5064,7 @@
         <v>12</v>
       </c>
       <c r="BB25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC25" t="n">
         <v>16</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-19-2014-15</t>
+          <t>2015-03-19</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>5.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE26" t="n">
         <v>5</v>
@@ -5137,7 +5204,7 @@
         <v>2</v>
       </c>
       <c r="AN26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO26" t="n">
         <v>26</v>
@@ -5149,7 +5216,7 @@
         <v>1</v>
       </c>
       <c r="AR26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS26" t="n">
         <v>1</v>
@@ -5167,7 +5234,7 @@
         <v>26</v>
       </c>
       <c r="AX26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
@@ -5176,7 +5243,7 @@
         <v>2</v>
       </c>
       <c r="BA26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB26" t="n">
         <v>9</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-19-2014-15</t>
+          <t>2015-03-19</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-4.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
@@ -5319,7 +5386,7 @@
         <v>28</v>
       </c>
       <c r="AN27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO27" t="n">
         <v>1</v>
@@ -5331,7 +5398,7 @@
         <v>5</v>
       </c>
       <c r="AR27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS27" t="n">
         <v>9</v>
@@ -5352,10 +5419,10 @@
         <v>28</v>
       </c>
       <c r="AY27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AZ27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA27" t="n">
         <v>1</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-19-2014-15</t>
+          <t>2015-03-19</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E28" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F28" t="n">
         <v>25</v>
       </c>
       <c r="G28" t="n">
-        <v>0.621</v>
+        <v>0.627</v>
       </c>
       <c r="H28" t="n">
         <v>48.8</v>
@@ -5411,49 +5478,49 @@
         <v>38.5</v>
       </c>
       <c r="J28" t="n">
-        <v>83.90000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="K28" t="n">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0.363</v>
+        <v>0.366</v>
       </c>
       <c r="O28" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="P28" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.773</v>
+        <v>0.774</v>
       </c>
       <c r="R28" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="T28" t="n">
-        <v>43.5</v>
+        <v>43.4</v>
       </c>
       <c r="U28" t="n">
         <v>24.1</v>
       </c>
       <c r="V28" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="W28" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="X28" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y28" t="n">
         <v>4.7</v>
@@ -5471,13 +5538,13 @@
         <v>4.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="AE28" t="n">
         <v>9</v>
       </c>
       <c r="AF28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG28" t="n">
         <v>9</v>
@@ -5501,7 +5568,7 @@
         <v>14</v>
       </c>
       <c r="AN28" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AO28" t="n">
         <v>14</v>
@@ -5516,7 +5583,7 @@
         <v>26</v>
       </c>
       <c r="AS28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT28" t="n">
         <v>16</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-19-2014-15</t>
+          <t>2015-03-19</t>
         </is>
       </c>
     </row>
@@ -5653,10 +5720,10 @@
         <v>3.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF29" t="n">
         <v>10</v>
@@ -5683,10 +5750,10 @@
         <v>10</v>
       </c>
       <c r="AN29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP29" t="n">
         <v>5</v>
@@ -5725,7 +5792,7 @@
         <v>13</v>
       </c>
       <c r="BB29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC29" t="n">
         <v>9</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-19-2014-15</t>
+          <t>2015-03-19</t>
         </is>
       </c>
     </row>
@@ -5757,25 +5824,25 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E30" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F30" t="n">
         <v>37</v>
       </c>
       <c r="G30" t="n">
-        <v>0.456</v>
+        <v>0.448</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
       </c>
       <c r="I30" t="n">
-        <v>35.4</v>
+        <v>35.5</v>
       </c>
       <c r="J30" t="n">
-        <v>78.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K30" t="n">
         <v>0.449</v>
@@ -5784,7 +5851,7 @@
         <v>7.3</v>
       </c>
       <c r="M30" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="N30" t="n">
         <v>0.346</v>
@@ -5793,19 +5860,19 @@
         <v>16.7</v>
       </c>
       <c r="P30" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.724</v>
+        <v>0.725</v>
       </c>
       <c r="R30" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S30" t="n">
         <v>32</v>
       </c>
       <c r="T30" t="n">
-        <v>43.8</v>
+        <v>44</v>
       </c>
       <c r="U30" t="n">
         <v>20.1</v>
@@ -5814,7 +5881,7 @@
         <v>15.3</v>
       </c>
       <c r="W30" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X30" t="n">
         <v>6</v>
@@ -5826,19 +5893,19 @@
         <v>19</v>
       </c>
       <c r="AA30" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>94.7</v>
+        <v>95</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AE30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AF30" t="n">
         <v>18</v>
@@ -5850,13 +5917,13 @@
         <v>30</v>
       </c>
       <c r="AI30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ30" t="n">
         <v>29</v>
       </c>
       <c r="AK30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL30" t="n">
         <v>17</v>
@@ -5865,22 +5932,22 @@
         <v>17</v>
       </c>
       <c r="AN30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO30" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AP30" t="n">
         <v>15</v>
       </c>
       <c r="AQ30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT30" t="n">
         <v>12</v>
@@ -5892,25 +5959,25 @@
         <v>26</v>
       </c>
       <c r="AW30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ30" t="n">
         <v>7</v>
       </c>
       <c r="BA30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-19-2014-15</t>
+          <t>2015-03-19</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>1.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AE31" t="n">
         <v>12</v>
@@ -6056,13 +6123,13 @@
         <v>24</v>
       </c>
       <c r="AQ31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR31" t="n">
         <v>20</v>
       </c>
       <c r="AS31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT31" t="n">
         <v>11</v>
@@ -6074,7 +6141,7 @@
         <v>24</v>
       </c>
       <c r="AW31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX31" t="n">
         <v>17</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-19-2014-15</t>
+          <t>2015-03-19</t>
         </is>
       </c>
     </row>
